--- a/teacher_evaluation_forms/030_teacher_evaluation_form--teacher_evaluation_forms.xlsx
+++ b/teacher_evaluation_forms/030_teacher_evaluation_form--teacher_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'mr',_'label':_'mr',_'type':_'text',_'options':_[]}</t>
+          <t>mr</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Mr', 'label': 'Mr', 'type': 'text', 'options': []}</t>
+          <t>Mr</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'ms',_'label':_'ms',_'type':_'text',_'options':_[]}</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Ms', 'label': 'Ms', 'type': 'text', 'options': []}</t>
+          <t>Ms</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'dr',_'label':_'dr',_'type':_'text',_'options':_[]}</t>
+          <t>dr</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Dr', 'label': 'Dr', 'type': 'text', 'options': []}</t>
+          <t>Dr</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'scale_5',_'label':_'scale_5',_'type':_'select_one',_'options':_[]}</t>
+          <t>scale_5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'scale_5', 'label': 'Scale 5', 'type': 'select_one', 'options': []}</t>
+          <t>Scale 5</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'scale_7',_'label':_'scale_7',_'type':_'select_one',_'options':_[]}</t>
+          <t>scale_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'scale_7', 'label': 'Scale 7', 'type': 'select_one', 'options': []}</t>
+          <t>Scale 7</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'scale_9',_'label':_'scale_9',_'type':_'select_one',_'options':_[]}</t>
+          <t>scale_9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'scale_9', 'label': 'Scale 9', 'type': 'select_one', 'options': []}</t>
+          <t>Scale 9</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'scale_10',_'label':_'scale_10',_'type':_'select_one',_'options':_[]}</t>
+          <t>scale_10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'scale_10', 'label': 'Scale 10', 'type': 'select_one', 'options': []}</t>
+          <t>Scale 10</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'excellent',_'label':_'excellent',_'type':_'text',_'options':_[]}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'excellent', 'label': 'Excellent', 'type': 'text', 'options': []}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'good',_'label':_'good',_'type':_'text',_'options':_[]}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'good', 'label': 'Good', 'type': 'text', 'options': []}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'average',_'label':_'average',_'type':_'text',_'options':_[]}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'average', 'label': 'Average', 'type': 'text', 'options': []}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
